--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T15:02:05+00:00</t>
+    <t>2025-07-11T15:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then it should be only one official identifier {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1 or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1 or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6900" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6899" uniqueCount="857">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T15:14:34+00:00</t>
+    <t>2025-07-15T08:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,7 +1579,7 @@
     <t>Patient.identifier:INS-NIR.use</t>
   </si>
   <si>
-    <t>La valeur old permet d'identifier des INS désactivés (en cas de fusion d'identité pour résoudre des problèmes de doublonnage par exemple)</t>
+    <t>La valeur old permet d'identifier des INS désactivés (permettant de noter l'ancien INS-NIR en cas de changement de sexe par exemple)</t>
   </si>
   <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use-ins</t>
@@ -1727,6 +1727,9 @@
   </si>
   <si>
     <t>Patient.identifier:INS-NIA.use</t>
+  </si>
+  <si>
+    <t>La valeur old permet d'identifier des INS désactivés (en cas d'obtention d'un INS-NIR par exemple)</t>
   </si>
   <si>
     <t>temp</t>
@@ -17057,7 +17060,7 @@
         <v>380</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>381</v>
+        <v>539</v>
       </c>
       <c r="O120" t="s" s="2">
         <v>382</v>
@@ -17070,7 +17073,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -17087,11 +17090,9 @@
       <c r="X120" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="Y120" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>385</v>
+        <v>495</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -17141,7 +17142,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>389</v>
@@ -17189,7 +17190,7 @@
         <v>82</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>82</v>
@@ -17260,7 +17261,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>400</v>
@@ -17289,7 +17290,7 @@
         <v>132</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>402</v>
@@ -17308,7 +17309,7 @@
         <v>82</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>406</v>
@@ -17379,7 +17380,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>411</v>
@@ -17496,7 +17497,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>420</v>
@@ -17611,7 +17612,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>427</v>
@@ -17728,10 +17729,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17754,70 +17755,70 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q126" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="R126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q126" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="R126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17832,13 +17833,13 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17849,10 +17850,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17875,19 +17876,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17924,7 +17925,7 @@
         <v>82</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AC127" s="2"/>
       <c r="AD127" t="s" s="2">
@@ -17934,7 +17935,7 @@
         <v>117</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17949,16 +17950,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17966,13 +17967,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>82</v>
@@ -17994,19 +17995,19 @@
         <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -18055,7 +18056,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18070,16 +18071,16 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -18087,10 +18088,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18202,10 +18203,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18319,10 +18320,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18348,16 +18349,16 @@
         <v>172</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18367,7 +18368,7 @@
         <v>82</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>82</v>
@@ -18385,10 +18386,10 @@
         <v>261</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18406,7 +18407,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18430,7 +18431,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18438,10 +18439,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18467,13 +18468,13 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O132" t="s" s="2">
         <v>282</v>
@@ -18525,7 +18526,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18549,7 +18550,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18557,14 +18558,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18586,13 +18587,13 @@
         <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18642,7 +18643,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18657,7 +18658,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
@@ -18666,7 +18667,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18674,14 +18675,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18703,13 +18704,13 @@
         <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18759,7 +18760,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18774,7 +18775,7 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -18783,7 +18784,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18791,10 +18792,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18820,10 +18821,10 @@
         <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18874,7 +18875,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18889,7 +18890,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
@@ -18898,7 +18899,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18906,10 +18907,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18935,10 +18936,10 @@
         <v>104</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18989,7 +18990,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19004,7 +19005,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -19013,7 +19014,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -19021,10 +19022,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19050,14 +19051,14 @@
         <v>341</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19106,7 +19107,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19130,7 +19131,7 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -19138,13 +19139,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>82</v>
@@ -19166,19 +19167,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19227,7 +19228,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19242,16 +19243,16 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19259,10 +19260,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19374,10 +19375,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19489,13 +19490,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>82</v>
@@ -19517,13 +19518,13 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19606,10 +19607,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19635,16 +19636,16 @@
         <v>172</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19672,10 +19673,10 @@
         <v>261</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19693,7 +19694,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19717,7 +19718,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19725,10 +19726,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19754,13 +19755,13 @@
         <v>104</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O143" t="s" s="2">
         <v>282</v>
@@ -19812,7 +19813,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19836,7 +19837,7 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19844,14 +19845,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19873,13 +19874,13 @@
         <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19929,7 +19930,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19944,7 +19945,7 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>82</v>
@@ -19953,7 +19954,7 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -19961,14 +19962,14 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19990,13 +19991,13 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20046,7 +20047,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20061,7 +20062,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>82</v>
@@ -20070,7 +20071,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -20078,10 +20079,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20107,10 +20108,10 @@
         <v>104</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20161,7 +20162,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20176,7 +20177,7 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20185,7 +20186,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20193,10 +20194,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20222,10 +20223,10 @@
         <v>104</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20276,7 +20277,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20291,7 +20292,7 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>82</v>
@@ -20300,7 +20301,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20308,10 +20309,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20337,14 +20338,14 @@
         <v>341</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20393,7 +20394,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20417,7 +20418,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20425,10 +20426,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20451,19 +20452,19 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20512,7 +20513,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20527,16 +20528,16 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20544,10 +20545,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20573,16 +20574,16 @@
         <v>172</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20611,7 +20612,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20629,7 +20630,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20644,16 +20645,16 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -20661,10 +20662,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20687,19 +20688,19 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20748,7 +20749,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20763,27 +20764,27 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20806,19 +20807,19 @@
         <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20867,7 +20868,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20882,7 +20883,7 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>108</v>
@@ -20891,7 +20892,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20899,10 +20900,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20928,16 +20929,16 @@
         <v>240</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20986,7 +20987,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21001,16 +21002,16 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -21018,10 +21019,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21047,14 +21048,14 @@
         <v>390</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21083,7 +21084,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>82</v>
@@ -21101,7 +21102,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21116,16 +21117,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21133,10 +21134,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21159,19 +21160,19 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21220,7 +21221,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21235,7 +21236,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>108</v>
@@ -21244,7 +21245,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21252,10 +21253,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21278,19 +21279,19 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21339,7 +21340,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21354,7 +21355,7 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>108</v>
@@ -21363,7 +21364,7 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21371,10 +21372,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21397,19 +21398,19 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21458,7 +21459,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21470,10 +21471,10 @@
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>108</v>
@@ -21490,10 +21491,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21605,10 +21606,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21718,13 +21719,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="B160" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="B160" t="s" s="2">
-        <v>729</v>
-      </c>
       <c r="C160" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>82</v>
@@ -21746,13 +21747,13 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21835,13 +21836,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>82</v>
@@ -21863,13 +21864,13 @@
         <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21952,14 +21953,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21981,10 +21982,10 @@
         <v>111</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>114</v>
@@ -22039,7 +22040,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22071,10 +22072,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22100,14 +22101,14 @@
         <v>390</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22135,10 +22136,10 @@
         <v>154</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22154,7 +22155,7 @@
         <v>117</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22169,7 +22170,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>108</v>
@@ -22178,7 +22179,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22186,13 +22187,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>82</v>
@@ -22217,14 +22218,14 @@
         <v>390</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22253,7 +22254,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22271,7 +22272,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22286,7 +22287,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>108</v>
@@ -22295,7 +22296,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22303,13 +22304,13 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>82</v>
@@ -22334,14 +22335,14 @@
         <v>390</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22370,7 +22371,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22388,7 +22389,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22403,7 +22404,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>108</v>
@@ -22412,7 +22413,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22420,10 +22421,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22446,17 +22447,17 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22505,7 +22506,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22520,7 +22521,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>108</v>
@@ -22529,7 +22530,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22537,10 +22538,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22563,19 +22564,19 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22624,7 +22625,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22639,7 +22640,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>108</v>
@@ -22648,7 +22649,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22656,10 +22657,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22682,17 +22683,17 @@
         <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22741,7 +22742,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22756,7 +22757,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>108</v>
@@ -22765,7 +22766,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -22773,10 +22774,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22802,14 +22803,14 @@
         <v>172</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22837,10 +22838,10 @@
         <v>261</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
@@ -22858,7 +22859,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22873,7 +22874,7 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>108</v>
@@ -22882,7 +22883,7 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -22890,10 +22891,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22919,14 +22920,14 @@
         <v>428</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -22975,7 +22976,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22984,13 +22985,13 @@
         <v>90</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>108</v>
@@ -22999,7 +23000,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>82</v>
@@ -23007,10 +23008,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23036,10 +23037,10 @@
         <v>341</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23090,7 +23091,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23105,7 +23106,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>108</v>
@@ -23122,10 +23123,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23148,19 +23149,19 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23209,7 +23210,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23224,10 +23225,10 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>82</v>
@@ -23241,10 +23242,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23356,10 +23357,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23473,14 +23474,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23502,10 +23503,10 @@
         <v>111</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>114</v>
@@ -23560,7 +23561,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23592,10 +23593,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23621,16 +23622,16 @@
         <v>390</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -23679,7 +23680,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>90</v>
@@ -23694,16 +23695,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23711,10 +23712,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23737,19 +23738,19 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>82</v>
@@ -23798,7 +23799,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23813,16 +23814,16 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -23830,14 +23831,14 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23856,16 +23857,16 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23915,7 +23916,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23930,7 +23931,7 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>108</v>
@@ -23939,7 +23940,7 @@
         <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
@@ -23947,10 +23948,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23973,19 +23974,19 @@
         <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24034,7 +24035,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24049,10 +24050,10 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>82</v>
@@ -24066,10 +24067,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24092,19 +24093,19 @@
         <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24153,7 +24154,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24168,7 +24169,7 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>108</v>
@@ -24185,10 +24186,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24300,10 +24301,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24417,14 +24418,14 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24446,10 +24447,10 @@
         <v>111</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>114</v>
@@ -24504,7 +24505,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24536,10 +24537,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24562,16 +24563,16 @@
         <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24621,7 +24622,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>90</v>
@@ -24645,7 +24646,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
@@ -24653,10 +24654,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24682,10 +24683,10 @@
         <v>172</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -24715,10 +24716,10 @@
         <v>261</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>82</v>
@@ -24736,7 +24737,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>90</v>
@@ -24751,7 +24752,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>108</v>

--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-15T08:52:52+00:00</t>
+    <t>2025-07-17T15:24:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1 or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1 or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -1579,6 +1579,9 @@
     <t>Patient.identifier:INS-NIR.use</t>
   </si>
   <si>
+    <t>official | old</t>
+  </si>
+  <si>
     <t>La valeur old permet d'identifier des INS désactivés (permettant de noter l'ancien INS-NIR en cas de changement de sexe par exemple)</t>
   </si>
   <si>
@@ -1730,9 +1733,6 @@
   </si>
   <si>
     <t>La valeur old permet d'identifier des INS désactivés (en cas d'obtention d'un INS-NIR par exemple)</t>
-  </si>
-  <si>
-    <t>temp</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIA.type</t>
@@ -13885,13 +13885,13 @@
         <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>379</v>
+        <v>494</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>380</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>382</v>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13973,7 +13973,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>389</v>
@@ -14021,7 +14021,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14039,10 +14039,10 @@
         <v>154</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -14092,7 +14092,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>400</v>
@@ -14121,7 +14121,7 @@
         <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M95" t="s" s="2">
         <v>402</v>
@@ -14211,7 +14211,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>411</v>
@@ -14328,7 +14328,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>420</v>
@@ -14443,7 +14443,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>427</v>
@@ -14560,13 +14560,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
@@ -14591,7 +14591,7 @@
         <v>360</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>362</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>374</v>
@@ -14794,7 +14794,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>376</v>
@@ -14911,7 +14911,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>378</v>
@@ -15030,7 +15030,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>389</v>
@@ -15078,7 +15078,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -15096,10 +15096,10 @@
         <v>154</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -15149,7 +15149,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>400</v>
@@ -15178,7 +15178,7 @@
         <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>402</v>
@@ -15197,7 +15197,7 @@
         <v>82</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>406</v>
@@ -15268,7 +15268,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>411</v>
@@ -15385,7 +15385,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>420</v>
@@ -15500,7 +15500,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>427</v>
@@ -15617,13 +15617,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>82</v>
@@ -15648,7 +15648,7 @@
         <v>360</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>362</v>
@@ -15736,7 +15736,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>374</v>
@@ -15851,7 +15851,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>376</v>
@@ -15968,7 +15968,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>378</v>
@@ -16087,7 +16087,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>389</v>
@@ -16135,7 +16135,7 @@
         <v>82</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>82</v>
@@ -16153,10 +16153,10 @@
         <v>154</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16206,7 +16206,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>400</v>
@@ -16235,7 +16235,7 @@
         <v>132</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>402</v>
@@ -16254,7 +16254,7 @@
         <v>82</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>406</v>
@@ -16325,7 +16325,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>411</v>
@@ -16442,7 +16442,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>420</v>
@@ -16557,7 +16557,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>427</v>
@@ -16674,13 +16674,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16705,7 +16705,7 @@
         <v>360</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M117" t="s" s="2">
         <v>362</v>
@@ -16793,7 +16793,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>374</v>
@@ -16908,7 +16908,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>376</v>
@@ -17025,7 +17025,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>378</v>
@@ -17054,13 +17054,13 @@
         <v>172</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>379</v>
+        <v>494</v>
       </c>
       <c r="M120" t="s" s="2">
         <v>380</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O120" t="s" s="2">
         <v>382</v>
@@ -17073,7 +17073,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -17208,10 +17208,10 @@
         <v>154</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>

--- a/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-update-patient-identifiers/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-17T15:24:19+00:00</t>
+    <t>2025-07-19T09:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1 or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'temp').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1).exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
